--- a/report/系统接入工作量评估.xlsx
+++ b/report/系统接入工作量评估.xlsx
@@ -334,7 +334,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1961,7 +1960,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>附件接入</t>
@@ -1969,7 +1968,7 @@
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
-          <t>每类非结构化源接入 + SHA-256 台账核对 + SAS 链路验证</t>
+          <t>源端摸底（位置/总量/命名规则）+ 业务键映射（文件 ↔ 业务表主键，登记 attachment_index）+ SHA-256 台账对账 + SAS 预览/下载链路验证</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
@@ -1979,7 +1978,7 @@
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>按附件类型数计（录音/图片/凭证各算一类）</t>
+          <t>文件搬运本身由 Storage Mover 自动完成、不计人天；成本在"搬完之后按业务记录找到附件"——每类源的映射规则不同（录音↔call_id、附件↔fileupload 表），故按类型计。有元数据表的（如 Dspot photo_info）取低值，映射需挖掘的（CC 录音/微信）取高值</t>
         </is>
       </c>
     </row>

--- a/report/系统接入工作量评估.xlsx
+++ b/report/系统接入工作量评估.xlsx
@@ -10,6 +10,7 @@
     <sheet name="分系统评估明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="工作量构成模型" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="汇总与风险" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="云资源成本估算" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +126,12 @@
       <color rgb="0064748B"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -195,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -256,6 +263,18 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -775,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -795,6 +814,7 @@
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -897,6 +917,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>关键评估假设（人天口径）</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -974,6 +999,11 @@
           <t>字段量全量最大</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>实测 1,253 表/24,620 字段；假设垃圾表（bak/temp/_Old）约 40%，审表按 ~600 张有效表估；热表 15~30 张配查询；附件 3 类；勾表评审 2 轮</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1055,6 +1085,11 @@
           <t>结构未知，拿到 DDL 后修正</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>结构未知：按中等（200~450 表）假设，先 DDL 导出定档后修正；热表 10~20 张；附件 1 类待确认</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -1132,6 +1167,11 @@
           <t>varchar 6,046 / longtext 381</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>实测 852 表/14,208 字段；假设 381 个 longtext/JSON 逐表决策"可查 vs 仅归档"；热表 15~25 张；素材附件 2~3 类；勾表 2 轮</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -1209,6 +1249,11 @@
           <t>最小系统之一</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>实测 227 表/2,231 字段；假设审批链关联表（AR_WFI_*）完整可读；热表 8~15 张；附件 2 类（审批附件+FOC 凭证）</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -1286,6 +1331,11 @@
           <t>ABP 框架系统</t>
         </is>
       </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>实测 557 表（含 Abp* 框架表约 1/3，需排除）；热表 10~20 张；健康报告附件 1~2 类；脱敏字段按 PII 正则扫描结果定</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -1367,6 +1417,11 @@
           <t>结构未知，先按中等预估</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>结构未知：按中等假设；SFE 数据敏感度参考 BPM；先结构发现后修正</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -1448,6 +1503,11 @@
           <t>结构未知，偏简单~中等预估</t>
         </is>
       </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>结构未知：内容型系统按简单~中等假设；推文/课程素材附件量待确认</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -1529,6 +1589,11 @@
           <t>结构未知，偏简单~中等预估</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>结构未知：按简单~中等假设；跟台数据量与附件待确认</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="4" t="n">
@@ -1606,6 +1671,11 @@
           <t>审批链完整性是验收红线</t>
         </is>
       </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>实测 374 表（含 Abp* 框架表）；假设审批链/审计表全量保留；发票+合同+资质附件 3 类；可能触发法定保留</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -1683,6 +1753,11 @@
           <t>最小系统</t>
         </is>
       </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>实测 123 表；photo/video 元数据表可直接映射（取低值）；附件 1~2 类</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -1758,6 +1833,11 @@
       <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>关联完整性是验收红线</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>实测 424 表（an+pnd 两库）；假设编码关联 join（条码-箱码-批次）逐一验证；条码图片附件 1~2 类</t>
         </is>
       </c>
     </row>
@@ -1815,6 +1895,11 @@
       <c r="Q16" s="15" t="inlineStr">
         <is>
           <t>2 人并行可压至 3.5~5 个月</t>
+        </is>
+      </c>
+      <c r="R16" s="14" t="inlineStr">
+        <is>
+          <t>共同假设：源库只读账号与 NAT 白名单已办妥；业务接口人可配合 1~2 轮勾表评审；B2 平台底座已建成</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2396,12 +2481,720 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>· 云资源成本（假设场景）见《云资源成本估算》Sheet：存储 ≈¥0.10~0.32 万/月 + 查询共享封顶 ≈¥0.59 万/月；首次入湖 ETL 一次性 ≈¥1.6~6.3 万</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A22:C22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>分系统云资源成本估算 · 假设场景（B2 湖仓 · Azure 列表价 $1=¥7.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>场景假设：湖存 Hot/Cool 混合 ¥90~150/TB·月 · 查询 Databricks Serverless X-Small ¥30/小时（6DBU×$0.7）· 查询时长 = 假设每天在线小时 × 22 工作日 · 首次入湖 ETL ¥1,500~3,000/TB（四层转换+Z-Order+首次合并，一次性）· 数据量为按系统类型推估，待实测修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>系统</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>假设数据量（TB）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>查询假设（小时/天）</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>存储（元/月）</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>查询计算（元/月）</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>首次入湖 ETL（一次性·元）</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>月度合计（存储+查询）</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Caring Center（CC）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2.5 ~ 4</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>2 ~ 3</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>225 ~ 600</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1,320 ~ 1,980</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>3,750 ~ 12,000</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>1,545 ~ 2,580</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>录音+微信+工单附件占比高，数据量最大</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>NGCRM</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>45 ~ 150</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>330.0 ~ 660</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>750 ~ 3,000</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>375.0 ~ 810</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>结构未知，按 0.5~1 TB 推估</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>ADC MA</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1.5 ~ 3</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1.5 ~ 2</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>135 ~ 450</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>990.0 ~ 1,320</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2,250 ~ 9,000</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>1,125.0 ~ 1,770</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>活动图片/素材附件多</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Eflow</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>45 ~ 150</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>330.0 ~ 660</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>750 ~ 3,000</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>375.0 ~ 810</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>交易+审批流，附件中等</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1 ~ 2</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1.5</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>90 ~ 300</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>330.0 ~ 990.0</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>1,500 ~ 6,000</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>420.0 ~ 1,290.0</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>健康报告附件</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>AMD SFE</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>45 ~ 150</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>330.0 ~ 660</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>750 ~ 3,000</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>375.0 ~ 810</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>结构未知，按中等推估</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>HF</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1.5</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>45 ~ 225</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>330.0 ~ 660</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>750 ~ 4,500</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>375.0 ~ 885</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>推文/课程素材，附件量大</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>VAS SFE</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>0.3 ~ 0.8</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>0.3 ~ 0.5</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>27 ~ 120</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>198.0 ~ 330.0</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>450 ~ 2,400</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>225.0 ~ 450.0</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>活动/跟台数据，量小</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>BPM</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1 ~ 2</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>1 ~ 1.5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>90 ~ 300</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>660 ~ 990.0</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>1,500 ~ 6,000</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>750 ~ 1,290.0</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>发票影像/合同/资质附件多</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Dspot</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1.2</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>0.5 ~ 1</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>45 ~ 180</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>330.0 ~ 660</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>750 ~ 3,600</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>375.0 ~ 840</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>签到图片/视频</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>银河 an + pnd</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2 ~ 3.5</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>1 ~ 1.5</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>180 ~ 525</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>660 ~ 990.0</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>3,000 ~ 10,500</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>840 ~ 1,515.0</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>条码记录行数大，序列化数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr"/>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>合计（11 项）</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>10.8 ~ 21</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>972 ~ 3,150</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>≈5,900（共享去重）</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>16,200 ~ 63,000</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>6,872 ~ 9,050</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>查询逐系统直加会重复计数——12 系统共享同一仓库，按工作时段在线 198h 封顶 ≈ ¥5,900/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>校验与读数</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>总量 10.8~21 TB，与整体基线 20 TB 吻合；存储合计 ¥972~3,150/月 ≈ ¥0.10~0.32 万/月，与报告口径（20TB → ¥0.18~0.30 万）一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>查询合计若逐系统直加为 ¥5,808.0~9,900.0——但 12 系统共用一个 Serverless 仓库、在线时段重叠，实际按 198h/月封顶 ≈ ¥5,900（¥0.59 万）；系统越多、分摊越薄</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>首次入湖 ETL 为一次性：合计 ¥16,200~63,000（≈¥1.6~6.3 万），随迁移节奏分摊到各月；此后每月增量+维护约为一次性的 5~10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>数据量是本表最大的不确定项：由"表数 × 平均行宽 × 行数 + 附件量"推估，接入前应按源库实际占用（sp_spaceused / information_schema）校准，成本随 TB 线性修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>不含：元数据库/AKS/Key Vault 等共用底座（三方案均摊）、跨区流量、备份多副本溢价、企业折扣（EA 通常可再谈 15~30%）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/系统接入工作量评估.xlsx
+++ b/report/系统接入工作量评估.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -132,6 +132,11 @@
       <color rgb="00B45309"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="001E3A8A"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -176,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -198,11 +203,55 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -274,6 +323,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2506,695 +2560,1045 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>分系统云资源成本估算 · 假设场景（B2 湖仓 · Azure 列表价 $1=¥7.1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>场景假设：湖存 Hot/Cool 混合 ¥90~150/TB·月 · 查询 Databricks Serverless X-Small ¥30/小时（6DBU×$0.7）· 查询时长 = 假设每天在线小时 × 22 工作日 · 首次入湖 ETL ¥1,500~3,000/TB（四层转换+Z-Order+首次合并，一次性）· 数据量为按系统类型推估，待实测修正</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+          <t>分系统云资源成本估算 · 单价基准与假设场景（B2 湖仓 · Azure 列表价 $1=¥7.1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>数据量为按系统类型推估（待 sp_spaceused 实测校准）· 附件存储只按 TB 计、与附件类型无关（类型只影响人工映射工作量，见明细表假设列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>一、单价基准（官方列表价 → 折算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>计费项</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>官方单价</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>折算 / 场景</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>查询 · SQL Serverless</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>$0.70 / DBU（Premium）</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>X-Small = 6 DBU/h ≈ ¥30/小时</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>DBU 单价已含底层 VM，无第二笔基础设施账单；按仓库在线小时计费、按秒累计，空闲 ~10 分钟自动暂停归零</t>
+        </is>
+      </c>
+      <c r="E6" s="30" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="30" t="n"/>
+      <c r="H6" s="30" t="n"/>
+      <c r="I6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>查询 · 单次查询成本</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>扫 2GB ≈ 20~40 秒 ≈ ¥0.2~0.5/次；扫 5GB ≈ 1 分钟 ≈ ¥0.5~1/次</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>仓库热着时按扫描量线性；冷启动首查多几秒（不另收费）</t>
+        </is>
+      </c>
+      <c r="E7" s="30" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+      <c r="H7" s="30" t="n"/>
+      <c r="I7" s="31" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ETL 写侧 · Databricks Jobs</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>$0.30 / DBU + 底层 VM（按量）</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>全包折算 ¥1,500~3,000 / TB</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>含四层转换（RAW→SERVE 约 5~6TB 有效读写）+ Z-Order + 首次 Compaction；附件 URL/台账重写也在此列</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+      <c r="H8" s="30" t="n"/>
+      <c r="I8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>存储 · 湖存（结构化）</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Hot ¥131 / Cool ¥73 / Cold ¥33 每 TB·月</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Hot/Cool 混合 ≈ ¥90~150 / TB·月</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>在线可查需 Hot/Cool；分层后单价随生命周期下降</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="30" t="n"/>
+      <c r="I9" s="31" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>存储 · 附件 Blob（非结构化）</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>同上单价表</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Cool→Cold 混合 ≈ ¥40~90 / TB·月</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>比湖存便宜（不需在线扫描）；与湖分账户、生命周期自动降档</t>
+        </is>
+      </c>
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+      <c r="H10" s="30" t="n"/>
+      <c r="I10" s="31" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>二、多系统并发查询如何计费（按仓库实例计费，不按系统叠加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>情形</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>计费结果</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>A 在查，B 随后查（先后）</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>仍是 1 个仓库 ¥30/小时</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>计费对象是仓库实例；谁来查、查几个系统都不影响单价</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+      <c r="H14" s="30" t="n"/>
+      <c r="I14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>A、B 同时查，单仓库扛得住</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>仍是 ¥30/小时</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>X-Small 默认并发队列足够日常交互查询；排队不产生额外费用</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="30" t="n"/>
+      <c r="I15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>A、B 同时跑大查询，单仓库打满</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>自动扩第 2 实例 → 该时段 ¥60/小时</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>Serverless 自动横向扩容，并发回落自动缩回；只有打满的时段才翻倍</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+      <c r="H16" s="30" t="n"/>
+      <c r="I16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>空闲 ~10 分钟</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>自动暂停 → ¥0</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>暂停期间不收费；下次查询几秒唤醒</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+      <c r="H17" s="30" t="n"/>
+      <c r="I17" s="31" t="n"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>月度账单公式</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>≈ 在线小时 × ¥30 × 平均实例数</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>典型：8h/天 × 22 天 = 176h × 1 实例 ≈ ¥5,280/月；本表合计按 198h ≈ ¥5,900 封顶</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+      <c r="H18" s="30" t="n"/>
+      <c r="I18" s="31" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>三、分系统估算（查询列为分摊口径，非叠加计费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>系统</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>假设数据量（TB）</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>查询假设（小时/天）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>存储（元/月）</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>查询计算（元/月）</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>查询分摊（元/月·非叠加）</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>首次入湖 ETL（一次性·元）</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>月度合计（存储+查询）</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>月度合计（存储+查询分摊）</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>Caring Center（CC）</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>2.5 ~ 4</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>2 ~ 3</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>225 ~ 600</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1,320 ~ 1,980</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>3,750 ~ 12,000</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>1,545 ~ 2,580</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>录音+微信+工单附件占比高，数据量最大</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>NGCRM</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>45 ~ 150</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>330.0 ~ 660</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>750 ~ 3,000</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>375.0 ~ 810</t>
         </is>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>结构未知，按 0.5~1 TB 推估</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>ADC MA</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>1.5 ~ 3</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>1.5 ~ 2</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>135 ~ 450</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>990.0 ~ 1,320</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>2,250 ~ 9,000</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>1,125.0 ~ 1,770</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>活动图片/素材附件多</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>Eflow</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>45 ~ 150</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>330.0 ~ 660</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>750 ~ 3,000</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>375.0 ~ 810</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>交易+审批流，附件中等</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>DHT</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>1 ~ 2</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1.5</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>90 ~ 300</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>330.0 ~ 990.0</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>1,500 ~ 6,000</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>420.0 ~ 1,290.0</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>健康报告附件</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>AMD SFE</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>45 ~ 150</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>330.0 ~ 660</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>750 ~ 3,000</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>375.0 ~ 810</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>结构未知，按中等推估</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>HF</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1.5</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>45 ~ 225</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>330.0 ~ 660</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>750 ~ 4,500</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>375.0 ~ 885</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>推文/课程素材，附件量大</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>VAS SFE</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>0.3 ~ 0.8</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>0.3 ~ 0.5</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>27 ~ 120</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>198.0 ~ 330.0</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>450 ~ 2,400</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>225.0 ~ 450.0</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>活动/跟台数据，量小</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>BPM</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>1 ~ 2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>1 ~ 1.5</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>90 ~ 300</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>660 ~ 990.0</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>1,500 ~ 6,000</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>750 ~ 1,290.0</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>发票影像/合同/资质附件多</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>Dspot</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1.2</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>0.5 ~ 1</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>45 ~ 180</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>330.0 ~ 660</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>750 ~ 3,600</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>375.0 ~ 840</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>签到图片/视频</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>银河 an + pnd</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>2 ~ 3.5</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>1 ~ 1.5</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>180 ~ 525</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>660 ~ 990.0</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>3,000 ~ 10,500</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>840 ~ 1,515.0</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>条码记录行数大，序列化数据</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr"/>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="16" t="inlineStr"/>
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>合计（11 项）</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>10.8 ~ 21</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>972 ~ 3,150</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>≈5,900（共享去重）</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>≈5,900（共享封顶）</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>16,200 ~ 63,000</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>6,872 ~ 9,050</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>查询逐系统直加会重复计数——12 系统共享同一仓库，按工作时段在线 198h 封顶 ≈ ¥5,900/月</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>校验与读数</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>总量 10.8~21 TB，与整体基线 20 TB 吻合；存储合计 ¥972~3,150/月 ≈ ¥0.10~0.32 万/月，与报告口径（20TB → ¥0.18~0.30 万）一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>查询合计若逐系统直加为 ¥5,808.0~9,900.0——但 12 系统共用一个 Serverless 仓库、在线时段重叠，实际按 198h/月封顶 ≈ ¥5,900（¥0.59 万）；系统越多、分摊越薄</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>首次入湖 ETL 为一次性：合计 ¥16,200~63,000（≈¥1.6~6.3 万），随迁移节奏分摊到各月；此后每月增量+维护约为一次性的 5~10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>数据量是本表最大的不确定项：由"表数 × 平均行宽 × 行数 + 附件量"推估，接入前应按源库实际占用（sp_spaceused / information_schema）校准，成本随 TB 线性修正</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>⑤</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>不含：元数据库/AKS/Key Vault 等共用底座（三方案均摊）、跨区流量、备份多副本溢价、企业折扣（EA 通常可再谈 15~30%）</t>
-        </is>
-      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>查询列逐系统直加会重复计——12 系统共用仓库，按在线 176~198h × 1 实例封顶 ≈ ¥5,280~5,900/月；仅并发打满时段翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>四、校验与读数</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>① 总量 10.8~21 TB，与整体基线 20 TB 吻合；存储合计 ¥972~3,150/月，与报告口径（20TB → ¥0.18~0.30 万）一致</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="n"/>
+      <c r="C36" s="30" t="n"/>
+      <c r="D36" s="30" t="n"/>
+      <c r="E36" s="30" t="n"/>
+      <c r="F36" s="30" t="n"/>
+      <c r="G36" s="30" t="n"/>
+      <c r="H36" s="30" t="n"/>
+      <c r="I36" s="31" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>② 首次入湖 ETL 一次性 ¥16,200~63,000（≈¥1.6~6.3 万），随迁移节奏分摊；此后每月增量+维护约为一次性的 5~10%</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="30" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="30" t="n"/>
+      <c r="H37" s="30" t="n"/>
+      <c r="I37" s="31" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>③ 每系统「查询分摊」仅用于比较用量权重；真实账单 = 仓库在线时长 × ¥30 × 实例数，系统越多分摊越薄</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="n"/>
+      <c r="C38" s="30" t="n"/>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="30" t="n"/>
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="30" t="n"/>
+      <c r="H38" s="30" t="n"/>
+      <c r="I38" s="31" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>④ 数据量由「表数 × 行宽 × 行数 + 附件量」推估，接入前按源库实际占用校准，成本随 TB 线性修正</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="30" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="30" t="n"/>
+      <c r="H39" s="30" t="n"/>
+      <c r="I39" s="31" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>⑤ 不含：元数据库 / AKS / Key Vault 等共用底座、跨区流量、备份溢价、企业折扣（EA 通常可再谈 15~30%）</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="30" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="30" t="n"/>
+      <c r="H40" s="30" t="n"/>
+      <c r="I40" s="31" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B21:I21"/>
+  <mergeCells count="21">
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="D7:I7"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="D8:I8"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="D10:I10"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="D6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/系统接入工作量评估.xlsx
+++ b/report/系统接入工作量评估.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="分系统评估明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="工作量构成模型" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="汇总与风险" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="云资源成本估算" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分系统评估明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作量构成模型" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总与风险" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="云资源成本估算" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -406,13 +406,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -436,10 +436,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="93C5FD"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -463,10 +463,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E3A8A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -506,8 +506,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -533,7 +533,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -548,9 +548,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2560,7 +2560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3576,8 +3576,16 @@
       <c r="H40" s="30" t="n"/>
       <c r="I40" s="31" t="n"/>
     </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="29" t="inlineStr">
+        <is>
+          <t>⑥ Azure 现行政策：新建 Databricks 工作区仅 Premium 档可选——本表单价即 Premium 价（$0.70/$0.30/DBU）；UC / Serverless / NCC / 私有端点默认可用，无需为能力升级另付费，EA 折扣仍可谈</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="C17:I17"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A12:I12"/>

--- a/report/系统接入工作量评估.xlsx
+++ b/report/系统接入工作量评估.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="260">
   <si>
     <t>退役系统接入工作量评估 · 分系统明细</t>
   </si>
@@ -380,6 +380,9 @@
   </si>
   <si>
     <t>共同假设：源库只读账号与 NAT 白名单已办妥；业务接口人可配合 1~2 轮勾表评审；B2 平台底座已建成</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>单系统接入工作量构成</t>
@@ -1568,7 +1571,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1611,6 +1614,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2419,7 +2423,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2439,7 +2443,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.2" customHeight="1" spans="1:19">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2448,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="21" customFormat="1" ht="30" customHeight="1" spans="1:19">
+    <row r="4" s="22" customFormat="1" ht="30" customHeight="1" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -2514,10 +2518,10 @@
       <c r="D5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="24">
         <v>1253</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="24">
         <v>24620</v>
       </c>
       <c r="G5" s="15" t="s">
@@ -2564,10 +2568,10 @@
       <c r="D6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="24" t="s">
         <v>32</v>
       </c>
       <c r="G6" s="15" t="s">
@@ -2614,10 +2618,10 @@
       <c r="D7" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <v>852</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <v>14208</v>
       </c>
       <c r="G7" s="15" t="s">
@@ -2664,10 +2668,10 @@
       <c r="D8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <v>227</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <v>2231</v>
       </c>
       <c r="G8" s="15" t="s">
@@ -2714,10 +2718,10 @@
       <c r="D9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="24">
         <v>557</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <v>9422</v>
       </c>
       <c r="G9" s="15" t="s">
@@ -2764,10 +2768,10 @@
       <c r="D10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="24" t="s">
         <v>32</v>
       </c>
       <c r="G10" s="15" t="s">
@@ -2814,10 +2818,10 @@
       <c r="D11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="24" t="s">
         <v>32</v>
       </c>
       <c r="G11" s="15" t="s">
@@ -2864,10 +2868,10 @@
       <c r="D12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="24" t="s">
         <v>32</v>
       </c>
       <c r="G12" s="15" t="s">
@@ -2914,10 +2918,10 @@
       <c r="D13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="24">
         <v>374</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <v>7116</v>
       </c>
       <c r="G13" s="15" t="s">
@@ -2964,10 +2968,10 @@
       <c r="D14" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="24">
         <v>123</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <v>2483</v>
       </c>
       <c r="G14" s="15" t="s">
@@ -3014,10 +3018,10 @@
       <c r="D15" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="24">
         <v>424</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="24">
         <v>7204</v>
       </c>
       <c r="G15" s="15" t="s">
@@ -3052,35 +3056,35 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1" spans="1:19">
-      <c r="A16" s="24"/>
+      <c r="A16" s="25"/>
       <c r="B16" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>3810</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>67064</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="24" t="s">
+      <c r="H16" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="25" t="s">
         <v>32</v>
       </c>
       <c r="L16" s="16">
@@ -3089,12 +3093,17 @@
       <c r="M16" s="16">
         <v>191</v>
       </c>
-      <c r="N16" s="25" t="s">
+      <c r="N16" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="O16" s="25"/>
+      <c r="O16" s="26"/>
       <c r="P16" s="17" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="14:14">
+      <c r="N19" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3124,174 +3133,174 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1" spans="1:10">
-      <c r="A1" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="H1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>118</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:10">
       <c r="A4" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:10">
       <c r="A5" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>46</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:10">
       <c r="A6" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:10">
       <c r="A7" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" ht="80" spans="1:10">
       <c r="A8" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:10">
       <c r="A9" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:10">
       <c r="A10" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="19" t="s">
-        <v>162</v>
+      <c r="A12" s="20" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="20" t="s">
-        <v>163</v>
+      <c r="A13" s="21" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="20" t="s">
-        <v>164</v>
+      <c r="A14" s="21" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3307,7 +3316,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -3323,31 +3332,31 @@
   <sheetData>
     <row r="1" ht="18.4" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:9">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -3357,16 +3366,16 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:9">
       <c r="A6" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
@@ -3376,16 +3385,16 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:9">
       <c r="A7" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -3395,16 +3404,16 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -3414,16 +3423,16 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
@@ -3433,16 +3442,16 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
@@ -3452,7 +3461,7 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:9">
       <c r="A13" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:9">
@@ -3463,25 +3472,25 @@
         <v>3</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:9">
@@ -3492,25 +3501,25 @@
         <v>18</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:9">
@@ -3521,25 +3530,25 @@
         <v>29</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:9">
@@ -3550,25 +3559,25 @@
         <v>40</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:9">
@@ -3579,25 +3588,25 @@
         <v>51</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:9">
@@ -3608,25 +3617,25 @@
         <v>61</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:9">
@@ -3637,25 +3646,25 @@
         <v>70</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:9">
@@ -3666,25 +3675,25 @@
         <v>76</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9">
@@ -3695,25 +3704,25 @@
         <v>83</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:9">
@@ -3724,25 +3733,25 @@
         <v>88</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:9">
@@ -3753,25 +3762,25 @@
         <v>95</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:9">
@@ -3782,25 +3791,25 @@
         <v>104</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26" ht="50" customHeight="1" spans="1:9">
@@ -3808,29 +3817,32 @@
         <v>114</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D26" s="16" t="s">
         <v>32</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>258</v>
-      </c>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="H30" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="10">
